--- a/SuppXLS/Scen_NEW_Oil_crazy_COPY.xlsx
+++ b/SuppXLS/Scen_NEW_Oil_crazy_COPY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Folder\Project\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC324693-A82C-41F6-86C7-46C8ADD4803D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{286FD28A-5F8D-42E5-8D51-D7C22829C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -65,13 +65,7 @@
     <t>IMPOIL*,IMPGAS*</t>
   </si>
   <si>
-    <t>IMPELC*,IMPBIO*</t>
-  </si>
-  <si>
     <t>*2</t>
-  </si>
-  <si>
-    <t>*5</t>
   </si>
 </sst>
 </file>
@@ -466,7 +460,7 @@
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>8</v>
@@ -475,15 +469,7 @@
       <c r="J6" s="5"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>

--- a/SuppXLS/Scen_NEW_Oil_crazy_COPY.xlsx
+++ b/SuppXLS/Scen_NEW_Oil_crazy_COPY.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git Folder\Project\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{286FD28A-5F8D-42E5-8D51-D7C22829C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{572D1BF1-4084-4F63-A5EC-C51376FCDCE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,10 +62,10 @@
     <t>IRE_PRICE</t>
   </si>
   <si>
-    <t>IMPOIL*,IMPGAS*</t>
-  </si>
-  <si>
     <t>*2</t>
+  </si>
+  <si>
+    <t>IMPOIL*</t>
   </si>
 </sst>
 </file>
@@ -425,16 +425,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C4:J7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D62E8F-6796-4EC5-8C47-1F7A1C63F1BB}">
+  <dimension ref="C4:I6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
@@ -454,24 +454,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="D6" s="4"/>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
